--- a/artfynd/A 28152-2026 artfynd.xlsx
+++ b/artfynd/A 28152-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192182</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192178</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1003,6 +1018,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192180</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1115,6 +1135,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192181</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1227,6 +1252,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192197</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1344,6 +1374,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192177</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1461,6 +1496,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192185</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1578,6 +1618,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192186</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1695,6 +1740,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192187</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1812,6 +1862,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192189</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1929,6 +1984,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192191</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2046,6 +2106,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192192</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2163,6 +2228,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192194</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2280,6 +2350,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192196</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2397,6 +2472,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192201</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2514,6 +2594,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192202</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2631,6 +2716,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192205</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2748,6 +2838,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192208</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2865,6 +2960,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192209</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2982,8 +3082,35 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192210</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 28152-2026 artfynd.xlsx
+++ b/artfynd/A 28152-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135192182</v>
       </c>
       <c r="B2" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135192178</v>
       </c>
       <c r="B3" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>135192180</v>
       </c>
       <c r="B4" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>135192181</v>
       </c>
       <c r="B5" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>135192197</v>
       </c>
       <c r="B6" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>135192177</v>
       </c>
       <c r="B7" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>135192185</v>
       </c>
       <c r="B8" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>135192186</v>
       </c>
       <c r="B9" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v>135192187</v>
       </c>
       <c r="B10" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>135192189</v>
       </c>
       <c r="B11" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>135192191</v>
       </c>
       <c r="B12" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>135192192</v>
       </c>
       <c r="B13" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>135192194</v>
       </c>
       <c r="B14" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>135192196</v>
       </c>
       <c r="B15" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>135192201</v>
       </c>
       <c r="B16" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>135192202</v>
       </c>
       <c r="B17" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         <v>135192205</v>
       </c>
       <c r="B18" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2727,7 +2727,7 @@
         <v>135192208</v>
       </c>
       <c r="B19" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>135192209</v>
       </c>
       <c r="B20" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         <v>135192210</v>
       </c>
       <c r="B21" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 28152-2026 artfynd.xlsx
+++ b/artfynd/A 28152-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135192182</v>
       </c>
       <c r="B2" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135192178</v>
       </c>
       <c r="B3" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>135192180</v>
       </c>
       <c r="B4" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>135192181</v>
       </c>
       <c r="B5" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>135192197</v>
       </c>
       <c r="B6" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 28152-2026 artfynd.xlsx
+++ b/artfynd/A 28152-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ6"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1255,6 +1255,1836 @@
       <c r="AZ6" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135192197</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135192177</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>443811</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7054330</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>färska och äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192177</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135192185</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>443820</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7054190</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192185</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135192186</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>443803</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7054210</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192186</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135192187</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>443718</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7054140</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192187</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135192189</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>443720</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7054143</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192189</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135192191</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>443695</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7054137</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192191</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135192192</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>443659</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7054134</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192192</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135192194</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>443645</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7054087</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192194</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135192196</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>443792</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7054072</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192196</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135192201</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>443624</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7053780</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192201</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135192202</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>443571</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7053723</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>färska och äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192202</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135192205</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>443499</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7053702</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192205</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135192208</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>443476</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7053750</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192208</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135192209</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>443475</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7053752</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192209</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135192210</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>443497</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7053761</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192210</t>
         </is>
       </c>
     </row>
@@ -1265,6 +3095,21 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28152-2026 artfynd.xlsx
+++ b/artfynd/A 28152-2026 artfynd.xlsx
@@ -1263,7 +1263,7 @@
         <v>135192177</v>
       </c>
       <c r="B7" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>135192185</v>
       </c>
       <c r="B8" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>135192186</v>
       </c>
       <c r="B9" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v>135192187</v>
       </c>
       <c r="B10" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>135192189</v>
       </c>
       <c r="B11" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>135192191</v>
       </c>
       <c r="B12" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>135192192</v>
       </c>
       <c r="B13" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>135192194</v>
       </c>
       <c r="B14" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>135192196</v>
       </c>
       <c r="B15" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>135192201</v>
       </c>
       <c r="B16" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>135192202</v>
       </c>
       <c r="B17" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         <v>135192205</v>
       </c>
       <c r="B18" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2727,7 +2727,7 @@
         <v>135192208</v>
       </c>
       <c r="B19" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>135192209</v>
       </c>
       <c r="B20" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         <v>135192210</v>
       </c>
       <c r="B21" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 28152-2026 artfynd.xlsx
+++ b/artfynd/A 28152-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ6"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1255,6 +1255,1836 @@
       <c r="AZ6" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135192197</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135192177</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>443811</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7054330</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>färska och äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192177</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135192185</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>443820</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7054190</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192185</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135192186</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>443803</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7054210</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192186</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135192187</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>443718</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7054140</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192187</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135192189</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>443720</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7054143</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192189</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135192191</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>443695</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7054137</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192191</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135192192</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>443659</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7054134</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192192</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135192194</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>443645</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7054087</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192194</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135192196</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>443792</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7054072</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192196</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135192201</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>443624</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7053780</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192201</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135192202</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>443571</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7053723</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>färska och äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192202</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135192205</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>443499</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7053702</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192205</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135192208</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>443476</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7053750</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192208</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135192209</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>443475</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7053752</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192209</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135192210</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>443497</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7053761</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192210</t>
         </is>
       </c>
     </row>
@@ -1265,6 +3095,21 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28152-2026 artfynd.xlsx
+++ b/artfynd/A 28152-2026 artfynd.xlsx
@@ -1263,7 +1263,7 @@
         <v>135192177</v>
       </c>
       <c r="B7" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>135192185</v>
       </c>
       <c r="B8" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>135192186</v>
       </c>
       <c r="B9" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v>135192187</v>
       </c>
       <c r="B10" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>135192189</v>
       </c>
       <c r="B11" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>135192191</v>
       </c>
       <c r="B12" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>135192192</v>
       </c>
       <c r="B13" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>135192194</v>
       </c>
       <c r="B14" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>135192196</v>
       </c>
       <c r="B15" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>135192201</v>
       </c>
       <c r="B16" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>135192202</v>
       </c>
       <c r="B17" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         <v>135192205</v>
       </c>
       <c r="B18" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2727,7 +2727,7 @@
         <v>135192208</v>
       </c>
       <c r="B19" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>135192209</v>
       </c>
       <c r="B20" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         <v>135192210</v>
       </c>
       <c r="B21" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 28152-2026 artfynd.xlsx
+++ b/artfynd/A 28152-2026 artfynd.xlsx
@@ -1263,7 +1263,7 @@
         <v>135192177</v>
       </c>
       <c r="B7" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>135192185</v>
       </c>
       <c r="B8" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>135192186</v>
       </c>
       <c r="B9" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v>135192187</v>
       </c>
       <c r="B10" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>135192189</v>
       </c>
       <c r="B11" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>135192191</v>
       </c>
       <c r="B12" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>135192192</v>
       </c>
       <c r="B13" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>135192194</v>
       </c>
       <c r="B14" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>135192196</v>
       </c>
       <c r="B15" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>135192201</v>
       </c>
       <c r="B16" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>135192202</v>
       </c>
       <c r="B17" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         <v>135192205</v>
       </c>
       <c r="B18" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2727,7 +2727,7 @@
         <v>135192208</v>
       </c>
       <c r="B19" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>135192209</v>
       </c>
       <c r="B20" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         <v>135192210</v>
       </c>
       <c r="B21" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 28152-2026 artfynd.xlsx
+++ b/artfynd/A 28152-2026 artfynd.xlsx
@@ -1263,7 +1263,7 @@
         <v>135192177</v>
       </c>
       <c r="B7" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>135192185</v>
       </c>
       <c r="B8" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>135192186</v>
       </c>
       <c r="B9" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v>135192187</v>
       </c>
       <c r="B10" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>135192189</v>
       </c>
       <c r="B11" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>135192191</v>
       </c>
       <c r="B12" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>135192192</v>
       </c>
       <c r="B13" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>135192194</v>
       </c>
       <c r="B14" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>135192196</v>
       </c>
       <c r="B15" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>135192201</v>
       </c>
       <c r="B16" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>135192202</v>
       </c>
       <c r="B17" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         <v>135192205</v>
       </c>
       <c r="B18" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2727,7 +2727,7 @@
         <v>135192208</v>
       </c>
       <c r="B19" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>135192209</v>
       </c>
       <c r="B20" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         <v>135192210</v>
       </c>
       <c r="B21" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 28152-2026 artfynd.xlsx
+++ b/artfynd/A 28152-2026 artfynd.xlsx
@@ -1263,7 +1263,7 @@
         <v>135192177</v>
       </c>
       <c r="B7" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>135192185</v>
       </c>
       <c r="B8" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>135192186</v>
       </c>
       <c r="B9" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v>135192187</v>
       </c>
       <c r="B10" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>135192189</v>
       </c>
       <c r="B11" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>135192191</v>
       </c>
       <c r="B12" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>135192192</v>
       </c>
       <c r="B13" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>135192194</v>
       </c>
       <c r="B14" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>135192196</v>
       </c>
       <c r="B15" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>135192201</v>
       </c>
       <c r="B16" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>135192202</v>
       </c>
       <c r="B17" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         <v>135192205</v>
       </c>
       <c r="B18" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2727,7 +2727,7 @@
         <v>135192208</v>
       </c>
       <c r="B19" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>135192209</v>
       </c>
       <c r="B20" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         <v>135192210</v>
       </c>
       <c r="B21" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 28152-2026 artfynd.xlsx
+++ b/artfynd/A 28152-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ6"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1255,6 +1255,1836 @@
       <c r="AZ6" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135192197</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135192177</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>443811</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7054330</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>färska och äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192177</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135192185</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>443820</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7054190</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192185</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135192186</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>443803</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7054210</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192186</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135192187</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>443718</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7054140</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192187</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135192189</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>443720</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7054143</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192189</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135192191</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>443695</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7054137</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192191</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135192192</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>443659</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7054134</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192192</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135192194</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>443645</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7054087</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192194</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135192196</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>443792</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7054072</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192196</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135192201</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>443624</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7053780</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192201</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135192202</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>443571</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7053723</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>färska och äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192202</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135192205</v>
+      </c>
+      <c r="B18" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>443499</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7053702</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192205</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135192208</v>
+      </c>
+      <c r="B19" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>443476</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7053750</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192208</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135192209</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>443475</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7053752</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192209</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135192210</v>
+      </c>
+      <c r="B21" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>443497</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7053761</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192210</t>
         </is>
       </c>
     </row>
@@ -1265,6 +3095,21 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
